--- a/output/graficos_regionales_indicadores/plot_regional_grupos_e_rezmat_a_2018_la_araucania_sexo.xlsx
+++ b/output/graficos_regionales_indicadores/plot_regional_grupos_e_rezmat_a_2018_la_araucania_sexo.xlsx
@@ -46,7 +46,7 @@
     <t xml:space="preserve">Fecha de creación</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-09-30 04:02</t>
+    <t xml:space="preserve">2026-10-05 06:19</t>
   </si>
   <si>
     <t xml:space="preserve">Fuente</t>
@@ -469,7 +469,7 @@
         <v>6.6</v>
       </c>
       <c r="D2" s="2" t="n">
-        <v>1.6</v>
+        <v>1.7</v>
       </c>
     </row>
     <row r="3">
